--- a/artfynd/A 56435-2023 artfynd.xlsx
+++ b/artfynd/A 56435-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56435-2023 artfynd.xlsx
+++ b/artfynd/A 56435-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106183168</v>
+        <v>106183119</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772137.3059672532</v>
+        <v>772232</v>
       </c>
       <c r="R2" t="n">
-        <v>7237890.834779733</v>
+        <v>7237901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +750,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +783,7 @@
         <v>106183126</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772191.4921213581</v>
+        <v>772192</v>
       </c>
       <c r="R3" t="n">
-        <v>7237872.579895728</v>
+        <v>7237872</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106183119</v>
+        <v>106183168</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772232.0277000761</v>
+        <v>772137</v>
       </c>
       <c r="R4" t="n">
-        <v>7237901.274233547</v>
+        <v>7237891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,19 +960,9 @@
           <t>2019-09-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,6 +987,221 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106183124</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pitmanlidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>772222</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7237924</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106183179</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pitmanlidberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>772190</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7237967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56435-2023 artfynd.xlsx
+++ b/artfynd/A 56435-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106183119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106183126</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106183168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106183124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106183179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>